--- a/data/trans_bre/IP42B-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP42B-Clase-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 19,5</t>
+          <t>-7,03; 18,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 23,83</t>
+          <t>-6,01; 23,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,5; 17,52</t>
+          <t>-10,8; 17,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-29,66; 0,0</t>
+          <t>-29,06; 0,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-16,33; 22,33</t>
+          <t>-16,16; 22,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-16,48; 7,85</t>
+          <t>-16,29; 7,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 14,99</t>
+          <t>-1,94; 13,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-18,28; 3,34</t>
+          <t>-18,99; 3,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,91; 7,02</t>
+          <t>-11,94; 6,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 127,72</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 6,74</t>
+          <t>-7,3; 6,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 18,13</t>
+          <t>-1,91; 20,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 9,04</t>
+          <t>-4,54; 9,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-81,84; 341,93</t>
+          <t>-85,8; 450,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,97; 327,45</t>
+          <t>-21,73; 355,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-72,76; 425,69</t>
+          <t>-67,19; 451,4</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 29,49</t>
+          <t>-10,42; 30,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-18,37; 8,85</t>
+          <t>-19,26; 8,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 8,83</t>
+          <t>-5,13; 9,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 568,86</t>
+          <t>-70,15; 799,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-59,88; 65,83</t>
+          <t>-60,38; 54,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-66,55; 350,68</t>
+          <t>-60,28; 564,39</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-47,21; 68,49</t>
+          <t>-49,37; 64,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-25,8; 53,58</t>
+          <t>-23,8; 52,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-42,61; 22,47</t>
+          <t>-43,48; 22,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-68,67; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-61,15; 390,28</t>
+          <t>-57,98; 348,52</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-85,33; 136,4</t>
+          <t>-84,26; 188,07</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 6,63</t>
+          <t>-3,13; 6,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 8,38</t>
+          <t>-4,38; 7,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 4,98</t>
+          <t>-3,6; 4,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-42,13; 147,04</t>
+          <t>-40,39; 149,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-22,15; 79,27</t>
+          <t>-27,2; 70,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-37,88; 102,76</t>
+          <t>-40,73; 88,42</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP42B-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP42B-Clase-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 18,36</t>
+          <t>-7,06; 19,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 23,85</t>
+          <t>-5,2; 23,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 17,25</t>
+          <t>-11,52; 17,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-29,06; 0,0</t>
+          <t>-29,96; 0,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-16,16; 22,51</t>
+          <t>-15,48; 22,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-16,29; 7,53</t>
+          <t>-16,08; 7,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 13,27</t>
+          <t>-1,95; 14,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-18,99; 3,3</t>
+          <t>-18,27; 4,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 6,58</t>
+          <t>-11,47; 6,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 6,72</t>
+          <t>-6,5; 6,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 20,05</t>
+          <t>-0,54; 19,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 9,22</t>
+          <t>-3,94; 9,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-85,8; 450,64</t>
+          <t>-84,74; 325,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,73; 355,24</t>
+          <t>-15,6; 383,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-67,19; 451,4</t>
+          <t>-63,98; 542,65</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 30,13</t>
+          <t>-9,87; 30,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-19,26; 8,36</t>
+          <t>-18,24; 10,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 9,83</t>
+          <t>-5,16; 9,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-70,15; 799,64</t>
+          <t>-72,63; 878,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-60,38; 54,79</t>
+          <t>-60,58; 64,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-60,28; 564,39</t>
+          <t>-59,89; 499,98</t>
         </is>
       </c>
     </row>
@@ -1034,17 +1034,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-49,37; 64,58</t>
+          <t>-41,86; 68,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-23,8; 52,84</t>
+          <t>-24,16; 50,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-43,48; 22,78</t>
+          <t>-42,42; 24,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1054,12 +1054,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-57,98; 348,52</t>
+          <t>-53,51; 386,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-84,26; 188,07</t>
+          <t>-82,03; 232,78</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 6,88</t>
+          <t>-3,29; 6,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 7,8</t>
+          <t>-4,07; 7,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 4,77</t>
+          <t>-3,68; 4,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-40,39; 149,64</t>
+          <t>-40,9; 147,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-27,2; 70,6</t>
+          <t>-24,33; 69,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-40,73; 88,42</t>
+          <t>-40,45; 97,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP42B-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP42B-Clase-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 19,19</t>
+          <t>-7,06; 19,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 23,87</t>
+          <t>-7,19; 23,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 17,76</t>
+          <t>-10,5; 17,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-29,96; 0,0</t>
+          <t>-29,66; 0,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,48; 22,5</t>
+          <t>-16,33; 22,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-16,08; 7,29</t>
+          <t>-16,48; 7,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -799,12 +799,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-18,27; 4,1</t>
+          <t>-18,28; 3,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,47; 6,62</t>
+          <t>-11,91; 7,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 127,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 6,11</t>
+          <t>-6,3; 6,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 19,33</t>
+          <t>-2,45; 18,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 9,11</t>
+          <t>-4,41; 9,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-84,74; 325,34</t>
+          <t>-81,84; 341,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-15,6; 383,63</t>
+          <t>-27,97; 327,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-63,98; 542,65</t>
+          <t>-72,76; 425,69</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 30,33</t>
+          <t>-11,43; 29,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-18,24; 10,23</t>
+          <t>-18,37; 8,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 9,56</t>
+          <t>-5,93; 8,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-72,63; 878,7</t>
+          <t>-100,0; 568,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-60,58; 64,71</t>
+          <t>-59,88; 65,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-59,89; 499,98</t>
+          <t>-66,55; 350,68</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-41,86; 68,4</t>
+          <t>-47,21; 68,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-24,16; 50,9</t>
+          <t>-25,8; 53,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-42,42; 24,68</t>
+          <t>-42,61; 22,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-68,67; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-53,51; 386,04</t>
+          <t>-61,15; 390,28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-82,03; 232,78</t>
+          <t>-85,33; 136,4</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 6,96</t>
+          <t>-3,11; 6,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 7,8</t>
+          <t>-3,8; 8,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 4,96</t>
+          <t>-3,07; 4,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-40,9; 147,49</t>
+          <t>-42,13; 147,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-24,33; 69,87</t>
+          <t>-22,15; 79,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-40,45; 97,29</t>
+          <t>-37,88; 102,76</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP42B-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP42B-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,139 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>4,26</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>7,11</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,93</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>119,82%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>166,54%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>42,42%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>4.258580078327098</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>7.106130085160665</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2.925177448730935</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>1.198212944905569</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>1.665437649438206</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.4242197024519355</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-7,06; 19,5</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-7,19; 23,83</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-10,5; 17,52</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-7.055770936113463</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-7.194839374312901</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-10.50110390797223</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>19.50488443505423</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>23.82690646988971</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>17.52286382720938</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-9,73</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>3,7</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-3,08</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>37,76%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-37,11%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-29,66; 0,0</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-16,33; 22,33</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-16,48; 7,85</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-9.731933424443802</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>3.700324173106528</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-3.079567059364114</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.3776486327002956</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.3710978500631757</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>3,15</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-6,18</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-2,94</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>165,26%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-54,2%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-47,82%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-29.6578501156493</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-16.33108990410111</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-16.48278201232412</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-1,95; 14,99</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-18,28; 3,34</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-11,91; 7,02</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 127,72</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>22.32916970610857</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>7.851343507591976</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,239 +743,155 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,46</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>8,06</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2,07</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-8,32%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>86,76%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>44,17%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>3.148488230697918</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-6.183581818213765</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-2.943507294395989</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>1.652602524320065</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.5420100542114046</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.478202618462507</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-6,3; 6,74</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-2,45; 18,13</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-4,41; 9,04</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-81,84; 341,93</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-27,97; 327,45</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-72,76; 425,69</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-1.94979456823322</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-18.2799760677572</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-11.90702946534753</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>14.99297930244592</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.33660432733614</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>7.015697488738811</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="n">
+        <v>1.277231839455434</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>7,97</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-4,28</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,67</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>68,75%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-18,59%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>28,21%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-11,43; 29,49</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-18,37; 8,85</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-5,93; 8,83</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 568,86</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-59,88; 65,83</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-66,55; 350,68</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-0.4614317608086553</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>8.061847244523124</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>2.071426132823752</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.08320354457590549</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.8675506725977868</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.4416688019842049</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>12,5</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>13,39</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-9,87</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>29,59%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>40,62%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-28,33%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-6.298012721272442</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.454442029924475</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-4.411652561719472</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.8184076653497512</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.2797278894678123</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.7276022051548253</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-47,21; 68,49</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-25,8; 53,58</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-42,61; 22,47</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-68,67; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-61,15; 390,28</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-85,33; 136,4</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>6.737490089562552</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>18.12758166338956</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>9.042471796139727</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>3.419250368064705</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>3.274546295665011</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>4.256944014252706</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1074,77 +899,241 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>1,81</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2,06</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,57</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>27,73%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>14,99%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8,1%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>7.971732882457566</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-4.282581401439323</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.666836418031505</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>0.6874812862436118</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.1859387119179112</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.2820966957686446</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-3,11; 6,63</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-3,8; 8,38</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-3,07; 4,98</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-42,13; 147,04</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-22,15; 79,27</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-37,88; 102,76</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-11.43496992203281</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-18.3677999663011</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-5.931009495384779</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.5988415799586548</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.6654936663262525</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>29.48718992008597</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>8.850873971684276</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>8.831482692715522</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>5.68857300768776</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.6582960457436259</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>3.506765640969186</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>12.49840122115977</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>13.39084434011541</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-9.873254997847894</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.2959300028913225</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.4061928930517814</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.2832881155938617</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-47.20927236881828</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-25.79936910411788</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-42.60910055934063</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.6866920714986657</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.6114782612749418</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.8532505428926758</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>68.48851270436785</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>53.58355865444744</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>22.46597578253715</v>
+      </c>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="n">
+        <v>3.902804102587841</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1.364030839751186</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>1.806688600493451</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>2.056649599816521</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.5738543075502783</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>0.2773447644298069</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0.1499227826773408</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>0.08097888488788539</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-3.112194709763667</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-3.797115205605304</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-3.069441636659991</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>-0.4213407428407707</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.2215043075874653</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.378764122493667</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>6.62674022894159</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>8.381822047729733</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>4.980846653512087</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>1.470397755527151</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.7926592709595276</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>1.027637096739728</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1153,15 +1142,15 @@
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
